--- a/reports/App評論監測_資料庫.xlsx
+++ b/reports/App評論監測_資料庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K437"/>
+  <dimension ref="A1:L438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
           <t>priority</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -537,6 +542,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -590,6 +596,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -643,6 +650,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -696,6 +704,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -749,6 +758,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -802,6 +812,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -855,6 +866,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,6 +920,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -961,6 +974,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1014,6 +1028,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1067,6 +1082,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1120,6 +1136,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1173,6 +1190,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1226,6 +1244,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1279,6 +1298,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1332,6 +1352,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1385,6 +1406,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1438,6 +1460,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1491,6 +1514,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1544,6 +1568,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1597,6 +1622,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1650,6 +1676,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1703,6 +1730,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1756,6 +1784,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1809,6 +1838,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1862,6 +1892,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1915,6 +1946,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1968,6 +2000,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2021,6 +2054,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2074,6 +2108,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2127,6 +2162,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2180,6 +2216,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2233,6 +2270,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2286,6 +2324,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2339,6 +2378,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2392,6 +2432,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2445,6 +2486,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2498,6 +2540,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2551,6 +2594,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2604,6 +2648,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2657,6 +2702,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2710,6 +2756,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2763,6 +2810,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2816,6 +2864,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2869,6 +2918,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2922,6 +2972,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2975,6 +3026,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3028,6 +3080,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3081,6 +3134,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3134,6 +3188,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3187,6 +3242,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3240,6 +3296,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3293,6 +3350,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3346,6 +3404,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3399,6 +3458,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3452,6 +3512,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3505,6 +3566,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3558,6 +3620,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3611,6 +3674,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3664,6 +3728,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3717,6 +3782,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3770,6 +3836,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3823,6 +3890,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3876,6 +3944,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3929,6 +3998,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3982,6 +4052,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4035,6 +4106,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4088,6 +4160,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4141,6 +4214,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4194,6 +4268,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4247,6 +4322,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4300,6 +4376,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4353,6 +4430,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4406,6 +4484,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4459,6 +4538,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4512,6 +4592,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4565,6 +4646,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4618,6 +4700,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4671,6 +4754,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4724,6 +4808,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4777,6 +4862,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4830,6 +4916,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4883,6 +4970,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4936,6 +5024,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4989,6 +5078,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5042,6 +5132,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5095,6 +5186,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5148,6 +5240,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5201,6 +5294,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5254,6 +5348,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5307,6 +5402,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5360,6 +5456,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5413,6 +5510,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5466,6 +5564,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5519,6 +5618,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5572,6 +5672,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5625,6 +5726,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5678,6 +5780,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5731,6 +5834,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5784,6 +5888,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5837,6 +5942,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5890,6 +5996,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5943,6 +6050,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5996,6 +6104,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6049,6 +6158,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6102,6 +6212,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6155,6 +6266,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6208,6 +6320,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6261,6 +6374,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6314,6 +6428,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6367,6 +6482,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6420,6 +6536,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6473,6 +6590,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6526,6 +6644,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6579,6 +6698,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6632,6 +6752,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6685,6 +6806,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6738,6 +6860,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6791,6 +6914,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6844,6 +6968,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6897,6 +7022,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6950,6 +7076,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7003,6 +7130,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7056,6 +7184,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7109,6 +7238,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7162,6 +7292,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7215,6 +7346,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7268,6 +7400,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7321,6 +7454,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7374,6 +7508,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7427,6 +7562,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7480,6 +7616,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7533,6 +7670,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7586,6 +7724,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7639,6 +7778,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7692,6 +7832,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7745,6 +7886,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7798,6 +7940,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7851,6 +7994,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7904,6 +8048,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7957,6 +8102,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8010,6 +8156,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8063,6 +8210,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8116,6 +8264,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8169,6 +8318,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8222,6 +8372,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8275,6 +8426,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8328,6 +8480,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8381,6 +8534,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8434,6 +8588,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8487,6 +8642,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8540,6 +8696,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8593,6 +8750,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8646,6 +8804,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8699,6 +8858,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8752,6 +8912,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8805,6 +8966,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8858,6 +9020,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8911,6 +9074,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8964,6 +9128,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9017,6 +9182,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9070,6 +9236,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9123,6 +9290,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9176,6 +9344,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9229,6 +9398,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9282,6 +9452,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9335,6 +9506,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9388,6 +9560,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9441,6 +9614,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9494,6 +9668,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9547,6 +9722,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9600,6 +9776,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9653,6 +9830,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9706,6 +9884,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9759,6 +9938,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9812,6 +9992,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9865,6 +10046,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9918,6 +10100,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9971,6 +10154,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10024,6 +10208,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10077,6 +10262,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10130,6 +10316,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10183,6 +10370,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10236,6 +10424,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10289,6 +10478,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10342,6 +10532,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10395,6 +10586,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10448,6 +10640,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10501,6 +10694,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10554,6 +10748,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10607,6 +10802,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10660,6 +10856,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10713,6 +10910,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10766,6 +10964,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10819,6 +11018,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10872,6 +11072,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10925,6 +11126,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10978,6 +11180,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11031,6 +11234,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11084,6 +11288,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11137,6 +11342,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11190,6 +11396,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11243,6 +11450,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11296,6 +11504,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11349,6 +11558,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11402,6 +11612,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11455,6 +11666,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11508,6 +11720,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11561,6 +11774,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11614,6 +11828,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11667,6 +11882,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11720,6 +11936,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11773,6 +11990,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11829,6 +12047,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11882,6 +12101,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11935,6 +12155,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11988,6 +12209,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12041,6 +12263,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12094,6 +12317,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12147,6 +12371,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12200,6 +12425,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12253,6 +12479,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12306,6 +12533,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12360,6 +12588,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12413,6 +12642,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12466,6 +12696,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12519,6 +12750,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12572,6 +12804,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12627,6 +12860,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12680,6 +12914,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12733,6 +12968,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12786,6 +13022,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12840,6 +13077,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12895,6 +13133,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12948,6 +13187,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13001,6 +13241,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13054,6 +13295,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13107,6 +13349,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13160,6 +13403,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13213,6 +13457,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13266,6 +13511,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13319,6 +13565,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13372,6 +13619,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13425,6 +13673,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13478,6 +13727,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13532,6 +13782,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13585,6 +13836,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13638,6 +13890,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13691,6 +13944,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13744,6 +13998,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13797,6 +14052,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13850,6 +14106,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13903,6 +14160,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13956,6 +14214,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14009,6 +14268,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14062,6 +14322,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14115,6 +14376,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14168,6 +14430,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14221,6 +14484,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14274,6 +14538,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14327,6 +14592,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14380,6 +14646,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14433,6 +14700,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14486,6 +14754,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14539,6 +14808,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14592,6 +14862,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14645,6 +14916,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14698,6 +14970,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14751,6 +15024,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14804,6 +15078,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14857,6 +15132,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14910,6 +15186,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14963,6 +15240,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15016,6 +15294,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15069,6 +15348,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15122,6 +15402,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15175,6 +15456,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15228,6 +15510,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15281,6 +15564,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15334,6 +15618,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15387,6 +15672,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15440,6 +15726,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15493,6 +15780,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15546,6 +15834,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -15599,6 +15888,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -15652,6 +15942,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -15705,6 +15996,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15758,6 +16050,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15811,6 +16104,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15864,6 +16158,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15917,6 +16212,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15970,6 +16266,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16023,6 +16320,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16076,6 +16374,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16129,6 +16428,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16182,6 +16482,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -16235,6 +16536,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16288,6 +16590,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16341,6 +16644,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16394,6 +16698,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -16447,6 +16752,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -16500,6 +16806,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -16553,6 +16860,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -16606,6 +16914,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -16659,6 +16968,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -16712,6 +17022,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -16765,6 +17076,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -16818,6 +17130,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -16871,6 +17184,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -16924,6 +17238,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -16977,6 +17292,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -17030,6 +17346,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -17083,6 +17400,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -17136,6 +17454,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -17189,6 +17508,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -17242,6 +17562,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -17295,6 +17616,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -17348,6 +17670,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -17401,6 +17724,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -17454,6 +17778,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -17507,6 +17832,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -17560,6 +17886,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -17613,6 +17940,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -17666,6 +17994,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -17719,6 +18048,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -17772,6 +18102,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -17825,6 +18156,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -17878,6 +18210,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -17931,6 +18264,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -17984,6 +18318,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -18037,6 +18372,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -18090,6 +18426,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -18143,6 +18480,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -18196,6 +18534,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -18249,6 +18588,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -18302,6 +18642,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -18355,6 +18696,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -18408,6 +18750,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -18461,6 +18804,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -18514,6 +18858,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -18567,6 +18912,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -18620,6 +18966,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -18673,6 +19020,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -18726,6 +19074,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -18779,6 +19128,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -18832,6 +19182,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -18885,6 +19236,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -18938,6 +19290,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -18991,6 +19344,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -19044,6 +19398,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -19097,6 +19452,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -19150,6 +19506,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -19203,6 +19560,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -19256,6 +19614,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -19309,6 +19668,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -19362,6 +19722,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -19415,6 +19776,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -19468,6 +19830,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -19521,6 +19884,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -19574,6 +19938,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -19627,6 +19992,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -19680,6 +20046,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -19733,6 +20100,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -19786,6 +20154,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -19839,6 +20208,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -19892,6 +20262,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -19945,6 +20316,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -19998,6 +20370,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -20051,6 +20424,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -20104,6 +20478,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -20157,6 +20532,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -20210,6 +20586,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -20263,6 +20640,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -20316,6 +20694,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -20369,6 +20748,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -20422,6 +20802,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -20475,6 +20856,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -20528,6 +20910,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -20581,6 +20964,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -20634,6 +21018,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -20687,6 +21072,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -20740,6 +21126,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -20793,6 +21180,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -20846,6 +21234,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -20899,6 +21288,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -20952,6 +21342,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -21005,6 +21396,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -21058,6 +21450,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -21111,6 +21504,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -21164,6 +21558,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -21217,6 +21612,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -21270,6 +21666,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -21323,6 +21720,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -21376,6 +21774,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -21429,6 +21828,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -21482,6 +21882,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -21535,6 +21936,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -21588,6 +21990,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -21641,6 +22044,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -21694,6 +22098,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -21747,6 +22152,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -21800,6 +22206,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -21853,6 +22260,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -21906,6 +22314,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -21959,6 +22368,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -22012,6 +22422,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -22065,6 +22476,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -22118,6 +22530,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -22171,6 +22584,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -22224,6 +22638,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -22277,6 +22692,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -22330,6 +22746,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -22383,6 +22800,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22436,6 +22854,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -22489,6 +22908,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -22542,6 +22962,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -22595,6 +23016,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -22648,6 +23070,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -22701,6 +23124,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -22754,6 +23178,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -22807,6 +23232,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -22860,6 +23286,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -22913,6 +23340,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -22966,6 +23394,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -23019,6 +23448,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -23072,6 +23502,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -23125,6 +23556,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -23178,6 +23610,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -23231,6 +23664,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -23284,6 +23718,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -23337,6 +23772,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="L432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -23390,6 +23826,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -23443,6 +23880,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="L434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -23496,6 +23934,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -23549,6 +23988,7 @@
           <t>低</t>
         </is>
       </c>
+      <c r="L436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -23600,6 +24040,65 @@
       <c r="K437" t="inlineStr">
         <is>
           <t>高</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>TeamWalk</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>客服有在運做嘛？</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>5</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>👍🏻</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2026-03-17 04:51:45</t>
+        </is>
+      </c>
+      <c r="G438" t="b">
+        <v>0</v>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>13857356270</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>正面評價</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>非常滿意</t>
         </is>
       </c>
     </row>
